--- a/static/Data/Normalized_Abilities.xlsx
+++ b/static/Data/Normalized_Abilities.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29019"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6E4B68B-1FFD-49E1-A70A-A6E94BCD4275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7A02953-D8A9-4F70-9334-3CBDB234537A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12642" uniqueCount="5260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12642" uniqueCount="5258">
   <si>
     <t>MASTERY 1</t>
   </si>
@@ -15654,279 +15654,163 @@
     <t>DESCRIPTION: Specialized in Portals.</t>
   </si>
   <si>
-    <t>Starting Bonus</t>
-  </si>
-  <si>
-    <t>Starting Weapon</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: Start The Game with 5 Common Ore in inventory.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Lucky Charm Equipped.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Random Rare Scroll.
- STARTING WEAPON: 
-Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Strength or Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STARTING BONUS: 
-Start the Game with Supply as a Bonus Resource; You may always convert 10 Mana to 1 Supply; Supply is Uncapped.
- STARTING WEAPON: 
-Any Strength or Dexterity Weapon.
-</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Dexterity Weapon. Starting with a Knife grants a second one as well.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 5 Extra Throwing Knives.
-Any Dexterity Weapon.
-Starting with a Knife grants a second one as well.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Cello.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Strength Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Extra Dispersion.
- STARTING WEAPON: 
-Any Strength Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with the Fire Wavelength.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with Rage as a Resource; It Starts at 0 and is uncapped and stays at 0 outside of Combat; You gain 10 Rage when landing Basic Attacks; Max Mana is converted automatically to Max Health.
- STARTING WEAPON: 
-Any Strength Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Skill Point in Potion Crafting.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Extra Strength.
- STARTING WEAPON: 
-Any Strength Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Common Quiver or 5 Common Throwing Axes.
- STARTING WEAPON: 
-Any Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Extra Power.
- STARTING WEAPON: 
-Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Melee Dexterity Weapon. Starting with a Knife grants a second one as well.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STARTING BONUS: 
-Start the Game with 1 Extra Dexterity.
- STARTING WEAPON: 
-Any Melee Dexterity Weapon.
-Starting with a Knife grants a second one as well.
-</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Melee Strength/Dexterity Weapon. One-Handed Weapons gain a Shield or Buckler as well.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Extra Defense.
- STARTING WEAPON: 
-Any Melee Strength/Dexterity Weapon.
-One-Handed Weapons gain a Shield or Buckler as well.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 10 Extra Health and Mana.
- STARTING WEAPON: 
-Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 2 Random Rare Ingredients.
- STARTING WEAPON: 
-Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Potion of Health.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Random Common Ring.
- STARTING WEAPON: 
-Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 20 Extra Mana.
- STARTING WEAPON: 
-Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Extra Attunement Point; You may invest Attunement Points over your Level.
- STARTING WEAPON: 
-Any Power Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a new Faction: Inquisition
-WARNING: NOT FINAL
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Common Staff.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game Wavelengthless; with Focus Replacing Mana; Regenerate 5 Focus Per Resonance while in Combat at the Start of your Turn; Outside of Combat Focus is always Maxed.
- STARTING WEAPON: 
-Common Staff.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: No Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with nothing.
- STARTING WEAPON: 
-No Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Dexterity or Strength Weapon of Choice.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 20 Extra Health.
- STARTING WEAPON: 
-Dexterity or Strength Weapon of Choice.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Common Pouch.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Common Pouch.
- STARTING WEAPON: 
-Common Pistol or Rifle.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Common Pistol or Rifle.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Common Body Piece.
- STARTING WEAPON: 
-Any Strength Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 2 Random Common Items.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with +1 Might.
- STARTING WEAPON: 
-Any Melee Strength or Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Melee Strength or Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with +1 Wisdom.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with a Skeleton Weakling under your Banner.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game Wavelengthless with Soul replacing Mana; You Regenerate 5% Max Soul Per Resonance at the Start of each Day; While you have 0 Soul or below, you are Weakened and Vulnerable.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with an Hourglass Artifact.
- STARTING WEAPON: 
-Any Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 5 Cogs.
- STARTING WEAPON: 
-Any Power or Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Power or Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 5 Meat/Flour.
- STARTING WEAPON: 
-Any Melee Strength/Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Melee Strength/Dexterity Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING BONUS: 
-Start the Game with 1 Extra Mobility.
- STARTING WEAPON: 
-Any Melee Weapon.</t>
-  </si>
-  <si>
-    <t>STARTING WEAPON: Any Melee Weapon.</t>
+    <t>Starting Bonus:</t>
+  </si>
+  <si>
+    <t>Starting Weapon:</t>
+  </si>
+  <si>
+    <t>Start The Game with 5 Common Ore in inventory.</t>
+  </si>
+  <si>
+    <t>Any Common Strength or Dexterity Melee Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Lucky Charm Equipped.</t>
+  </si>
+  <si>
+    <t>Any Common Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Random Rare Scroll.</t>
+  </si>
+  <si>
+    <t>Any Common Power Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with Supply as a Bonus Resource; You may always convert 10 Mana to 1 Supply; Supply is Uncapped.</t>
+  </si>
+  <si>
+    <t>Any Common Strength or Dexterity Weapon; Starting with a Knife grants a second one as well.</t>
+  </si>
+  <si>
+    <t>Start the Game with 5 Extra Throwing Knives.</t>
+  </si>
+  <si>
+    <t>Any Common Dexterity Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Cello.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Extra Dispersion.</t>
+  </si>
+  <si>
+    <t>Any Common Strength Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with the Fire Wavelength.</t>
+  </si>
+  <si>
+    <t>Start the Game with Rage as a Resource; It Starts at 0 and is uncapped and stays at 0 outside of Combat; You gain 10 Rage when landing Basic Attacks; Max Mana is converted automatically to Max Health.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Skill Point in Potion Crafting.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Extra Strength.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Common Quiver or 5 Common Throwing Axes.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Extra Power.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Extra Dexterity.</t>
+  </si>
+  <si>
+    <t>Any Common Melee Dexterity Weapon; Any Common Melee Dexterity Weapon. Starting with a Knife grants a second one as well.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Extra Defense.</t>
+  </si>
+  <si>
+    <t>Any Common Melee Strength/Dexterity Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with 10 Extra Health and Mana.</t>
+  </si>
+  <si>
+    <t>Start the Game with 2 Random Rare Ingredients.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Potion of Health.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Random Common Ring.</t>
+  </si>
+  <si>
+    <t>Start the Game with 20 Extra Mana.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Extra Attunement Point; You may invest Attunement Points over your Level.</t>
+  </si>
+  <si>
+    <t>Start the Game with a new Faction: Inquisition WARNING: NOT FINAL</t>
+  </si>
+  <si>
+    <t>Start the Game Wavelengthless; with Focus Replacing Mana; Regenerate 5 Focus Per Resonance while in Combat at the Start of your Turn; Outside of Combat Focus is always Maxed.</t>
+  </si>
+  <si>
+    <t>Common Staff.</t>
+  </si>
+  <si>
+    <t>Start the Game with nothing.</t>
+  </si>
+  <si>
+    <t>No Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with 20 Extra Health.</t>
+  </si>
+  <si>
+    <t>Common Dexterity or Strength Weapon of Choice.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Common Pouch.</t>
+  </si>
+  <si>
+    <t>Common Pistol or Rifle.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Common Body Piece.</t>
+  </si>
+  <si>
+    <t>Start the Game with 2 Random Common Items.</t>
+  </si>
+  <si>
+    <t>Start the Game with +1 Might.</t>
+  </si>
+  <si>
+    <t>Any Common Melee Strength or Dexterity Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with +1 Wisdom.</t>
+  </si>
+  <si>
+    <t>Start the Game with a Skeleton Weakling under your Banner.</t>
+  </si>
+  <si>
+    <t>Start the Game Wavelengthless with Soul replacing Mana; You Regenerate 5% Max Soul Per Resonance at the Start of each Day; While you have 0 Soul or below, you are Weakened and Vulnerable.</t>
+  </si>
+  <si>
+    <t>Start the Game with an Hourglass Artifact.</t>
+  </si>
+  <si>
+    <t>Start the Game with 5 Cogs.</t>
+  </si>
+  <si>
+    <t>Any Common Power or Dexterity Weapon.</t>
+  </si>
+  <si>
+    <t>Start the Game with 5 Meat/Flour.</t>
+  </si>
+  <si>
+    <t>Start the Game with 1 Extra Mobility.</t>
+  </si>
+  <si>
+    <t>Any Common Melee Weapon.</t>
   </si>
 </sst>
 </file>
@@ -69550,422 +69434,422 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC1A932-88F5-4DB4-A909-D669479A9058}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="2" max="2" width="59.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="73.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="1"/>
     <col min="5" max="5" width="22.7109375" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5205</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>5206</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>5207</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>5208</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5209</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>5210</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5211</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>5212</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5213</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>5214</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5215</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="C6" s="1" t="s">
+        <v>5216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5216</v>
-      </c>
-      <c r="D7" s="1" t="s">
         <v>5217</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="C7" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5218</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="C8" s="1" t="s">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5219</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>5217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>5220</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5220</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>5221</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5221</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>5217</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>5222</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5222</v>
-      </c>
-      <c r="D12" s="1" t="s">
         <v>5223</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="C12" s="1" t="s">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5224</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>5210</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="C13" s="1" t="s">
+        <v>5216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5225</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>5226</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="C14" s="1" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>5226</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>5227</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>5228</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>5228</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>5229</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>5210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>5230</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>5210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="C17" s="1" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>5231</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="C18" s="1" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>5232</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>5210</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>5233</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>5210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="C20" s="1" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>5234</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>5210</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="C21" s="1" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>5235</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="C22" s="1" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>5236</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>5237</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="C23" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>5237</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>5238</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>5239</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>5239</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>5240</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>5241</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>5241</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>5242</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>5243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>5243</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>5244</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>5245</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>161</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>5246</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>5217</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>5245</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>5247</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>5246</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>5247</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>5248</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>5249</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>5250</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>5249</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
         <v>180</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>5251</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>5250</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
         <v>185</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>5252</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>5251</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
         <v>190</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>5253</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>5208</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>5252</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>5253</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>5254</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>5255</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
         <v>198</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>5256</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>5257</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>5255</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>5229</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
         <v>202</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>5258</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>5259</v>
+        <v>5256</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>5257</v>
       </c>
     </row>
   </sheetData>

--- a/static/Data/Normalized_Abilities.xlsx
+++ b/static/Data/Normalized_Abilities.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29019"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29101"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7A02953-D8A9-4F70-9334-3CBDB234537A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F0F756C-604E-4B91-B8F1-D454400AF94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="3" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12642" uniqueCount="5258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12642" uniqueCount="5260">
   <si>
     <t>MASTERY 1</t>
   </si>
@@ -15363,6 +15363,9 @@
     <t>DESCRIPTION: Use the powers of the frost to both freeze your opponents but to also protect and save yourself.</t>
   </si>
   <si>
+    <t>Solar Mage</t>
+  </si>
+  <si>
     <t>DESCRIPTION: Use the power of the sun to burn and blind your target.</t>
   </si>
   <si>
@@ -15400,6 +15403,9 @@
   </si>
   <si>
     <t>DESCRIPTION: Specialized in Rune enchantment to make his weapon or armor more efficient in combat; Consume Runes to unleash devastating Attacks.</t>
+  </si>
+  <si>
+    <t>Solar Knight</t>
   </si>
   <si>
     <t>DESCRIPTION: Harness the power of the Sun to blind and burn your opponents as you advance forward to punish with your knightly skills.</t>
@@ -68257,13 +68263,13 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>5108</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>5046</v>
       </c>
       <c r="C59" t="s">
-        <v>5108</v>
+        <v>5109</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -68274,7 +68280,7 @@
         <v>5050</v>
       </c>
       <c r="C60" t="s">
-        <v>5109</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -68285,7 +68291,7 @@
         <v>5052</v>
       </c>
       <c r="C61" t="s">
-        <v>5110</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -68296,7 +68302,7 @@
         <v>5046</v>
       </c>
       <c r="C62" t="s">
-        <v>5111</v>
+        <v>5112</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -68307,7 +68313,7 @@
         <v>5048</v>
       </c>
       <c r="C63" t="s">
-        <v>5112</v>
+        <v>5113</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -68318,7 +68324,7 @@
         <v>5046</v>
       </c>
       <c r="C64" t="s">
-        <v>5113</v>
+        <v>5114</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -68329,7 +68335,7 @@
         <v>5046</v>
       </c>
       <c r="C65" t="s">
-        <v>5114</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -68340,7 +68346,7 @@
         <v>5050</v>
       </c>
       <c r="C66" t="s">
-        <v>5115</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -68351,7 +68357,7 @@
         <v>5048</v>
       </c>
       <c r="C67" t="s">
-        <v>5116</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -68362,7 +68368,7 @@
         <v>5050</v>
       </c>
       <c r="C68" t="s">
-        <v>5117</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -68373,7 +68379,7 @@
         <v>5052</v>
       </c>
       <c r="C69" t="s">
-        <v>5118</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -68384,7 +68390,7 @@
         <v>5052</v>
       </c>
       <c r="C70" t="s">
-        <v>5119</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -68395,18 +68401,18 @@
         <v>5048</v>
       </c>
       <c r="C71" t="s">
-        <v>5120</v>
+        <v>5121</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>5122</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>5048</v>
       </c>
       <c r="C72" t="s">
-        <v>5121</v>
+        <v>5123</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -68417,7 +68423,7 @@
         <v>5046</v>
       </c>
       <c r="C73" t="s">
-        <v>5122</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -68428,7 +68434,7 @@
         <v>5052</v>
       </c>
       <c r="C74" t="s">
-        <v>5123</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -68439,7 +68445,7 @@
         <v>5048</v>
       </c>
       <c r="C75" t="s">
-        <v>5124</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -68450,7 +68456,7 @@
         <v>5052</v>
       </c>
       <c r="C76" t="s">
-        <v>5125</v>
+        <v>5127</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -68461,7 +68467,7 @@
         <v>5046</v>
       </c>
       <c r="C77" t="s">
-        <v>5126</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -68472,7 +68478,7 @@
         <v>5046</v>
       </c>
       <c r="C78" t="s">
-        <v>5127</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -68483,7 +68489,7 @@
         <v>5050</v>
       </c>
       <c r="C79" t="s">
-        <v>5128</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -68494,7 +68500,7 @@
         <v>5048</v>
       </c>
       <c r="C80" t="s">
-        <v>5129</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -68505,7 +68511,7 @@
         <v>5052</v>
       </c>
       <c r="C81" t="s">
-        <v>5130</v>
+        <v>5132</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -68516,7 +68522,7 @@
         <v>5052</v>
       </c>
       <c r="C82" t="s">
-        <v>5131</v>
+        <v>5133</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -68527,7 +68533,7 @@
         <v>5052</v>
       </c>
       <c r="C83" t="s">
-        <v>5132</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -68538,7 +68544,7 @@
         <v>5052</v>
       </c>
       <c r="C84" t="s">
-        <v>5133</v>
+        <v>5135</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -68549,7 +68555,7 @@
         <v>5052</v>
       </c>
       <c r="C85" t="s">
-        <v>5134</v>
+        <v>5136</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -68560,7 +68566,7 @@
         <v>5046</v>
       </c>
       <c r="C86" t="s">
-        <v>5135</v>
+        <v>5137</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -68571,7 +68577,7 @@
         <v>5046</v>
       </c>
       <c r="C87" t="s">
-        <v>5136</v>
+        <v>5138</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -68582,7 +68588,7 @@
         <v>5046</v>
       </c>
       <c r="C88" t="s">
-        <v>5137</v>
+        <v>5139</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -68593,7 +68599,7 @@
         <v>5048</v>
       </c>
       <c r="C89" t="s">
-        <v>5138</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -68604,7 +68610,7 @@
         <v>5048</v>
       </c>
       <c r="C90" t="s">
-        <v>5139</v>
+        <v>5141</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -68615,7 +68621,7 @@
         <v>5046</v>
       </c>
       <c r="C91" t="s">
-        <v>5140</v>
+        <v>5142</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -68626,7 +68632,7 @@
         <v>5046</v>
       </c>
       <c r="C92" t="s">
-        <v>5141</v>
+        <v>5143</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -68637,7 +68643,7 @@
         <v>5046</v>
       </c>
       <c r="C93" t="s">
-        <v>5142</v>
+        <v>5144</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -68648,7 +68654,7 @@
         <v>5048</v>
       </c>
       <c r="C94" t="s">
-        <v>5143</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -68659,7 +68665,7 @@
         <v>5050</v>
       </c>
       <c r="C95" t="s">
-        <v>5144</v>
+        <v>5146</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -68670,7 +68676,7 @@
         <v>5046</v>
       </c>
       <c r="C96" t="s">
-        <v>5145</v>
+        <v>5147</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -68681,7 +68687,7 @@
         <v>5048</v>
       </c>
       <c r="C97" t="s">
-        <v>5146</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -68692,7 +68698,7 @@
         <v>5048</v>
       </c>
       <c r="C98" t="s">
-        <v>5147</v>
+        <v>5149</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -68703,7 +68709,7 @@
         <v>5050</v>
       </c>
       <c r="C99" t="s">
-        <v>5148</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -68714,7 +68720,7 @@
         <v>5050</v>
       </c>
       <c r="C100" t="s">
-        <v>5149</v>
+        <v>5151</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -68722,10 +68728,10 @@
         <v>137</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>5150</v>
+        <v>5152</v>
       </c>
       <c r="C101" t="s">
-        <v>5151</v>
+        <v>5153</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -68733,10 +68739,10 @@
         <v>138</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>5150</v>
+        <v>5152</v>
       </c>
       <c r="C102" t="s">
-        <v>5152</v>
+        <v>5154</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -68747,7 +68753,7 @@
         <v>5052</v>
       </c>
       <c r="C103" t="s">
-        <v>5153</v>
+        <v>5155</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -68758,7 +68764,7 @@
         <v>5048</v>
       </c>
       <c r="C104" t="s">
-        <v>5154</v>
+        <v>5156</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -68769,7 +68775,7 @@
         <v>5048</v>
       </c>
       <c r="C105" t="s">
-        <v>5155</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -68780,7 +68786,7 @@
         <v>5046</v>
       </c>
       <c r="C106" t="s">
-        <v>5156</v>
+        <v>5158</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -68791,7 +68797,7 @@
         <v>5055</v>
       </c>
       <c r="C107" t="s">
-        <v>5157</v>
+        <v>5159</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -68802,7 +68808,7 @@
         <v>5055</v>
       </c>
       <c r="C108" t="s">
-        <v>5158</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -68813,7 +68819,7 @@
         <v>5055</v>
       </c>
       <c r="C109" t="s">
-        <v>5159</v>
+        <v>5161</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -68824,7 +68830,7 @@
         <v>5046</v>
       </c>
       <c r="C110" t="s">
-        <v>5160</v>
+        <v>5162</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -68835,7 +68841,7 @@
         <v>5055</v>
       </c>
       <c r="C111" t="s">
-        <v>5161</v>
+        <v>5163</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -68846,7 +68852,7 @@
         <v>5050</v>
       </c>
       <c r="C112" t="s">
-        <v>5162</v>
+        <v>5164</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -68857,7 +68863,7 @@
         <v>5048</v>
       </c>
       <c r="C113" t="s">
-        <v>5163</v>
+        <v>5165</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -68868,7 +68874,7 @@
         <v>5048</v>
       </c>
       <c r="C114" t="s">
-        <v>5164</v>
+        <v>5166</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -68879,7 +68885,7 @@
         <v>5052</v>
       </c>
       <c r="C115" t="s">
-        <v>5165</v>
+        <v>5167</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -68890,7 +68896,7 @@
         <v>5048</v>
       </c>
       <c r="C116" t="s">
-        <v>5166</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -68901,7 +68907,7 @@
         <v>5052</v>
       </c>
       <c r="C117" t="s">
-        <v>5167</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -68912,7 +68918,7 @@
         <v>5046</v>
       </c>
       <c r="C118" t="s">
-        <v>5168</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -68923,7 +68929,7 @@
         <v>5046</v>
       </c>
       <c r="C119" t="s">
-        <v>5169</v>
+        <v>5171</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -68934,7 +68940,7 @@
         <v>5046</v>
       </c>
       <c r="C120" t="s">
-        <v>5170</v>
+        <v>5172</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -68945,7 +68951,7 @@
         <v>5052</v>
       </c>
       <c r="C121" t="s">
-        <v>5171</v>
+        <v>5173</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -68956,7 +68962,7 @@
         <v>5046</v>
       </c>
       <c r="C122" t="s">
-        <v>5172</v>
+        <v>5174</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -68967,7 +68973,7 @@
         <v>5046</v>
       </c>
       <c r="C123" t="s">
-        <v>5173</v>
+        <v>5175</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -68978,7 +68984,7 @@
         <v>5046</v>
       </c>
       <c r="C124" t="s">
-        <v>5174</v>
+        <v>5176</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -68989,7 +68995,7 @@
         <v>5048</v>
       </c>
       <c r="C125" t="s">
-        <v>5175</v>
+        <v>5177</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -69000,7 +69006,7 @@
         <v>5052</v>
       </c>
       <c r="C126" t="s">
-        <v>5176</v>
+        <v>5178</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -69011,7 +69017,7 @@
         <v>5055</v>
       </c>
       <c r="C127" t="s">
-        <v>5177</v>
+        <v>5179</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -69022,7 +69028,7 @@
         <v>5052</v>
       </c>
       <c r="C128" t="s">
-        <v>5178</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -69033,7 +69039,7 @@
         <v>5052</v>
       </c>
       <c r="C129" t="s">
-        <v>5179</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -69044,7 +69050,7 @@
         <v>5046</v>
       </c>
       <c r="C130" t="s">
-        <v>5180</v>
+        <v>5182</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -69055,7 +69061,7 @@
         <v>5048</v>
       </c>
       <c r="C131" t="s">
-        <v>5181</v>
+        <v>5183</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -69066,7 +69072,7 @@
         <v>5048</v>
       </c>
       <c r="C132" t="s">
-        <v>5182</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -69077,7 +69083,7 @@
         <v>5046</v>
       </c>
       <c r="C133" t="s">
-        <v>5183</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -69088,7 +69094,7 @@
         <v>5048</v>
       </c>
       <c r="C134" t="s">
-        <v>5184</v>
+        <v>5186</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -69099,7 +69105,7 @@
         <v>5050</v>
       </c>
       <c r="C135" t="s">
-        <v>5185</v>
+        <v>5187</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -69110,7 +69116,7 @@
         <v>5052</v>
       </c>
       <c r="C136" t="s">
-        <v>5186</v>
+        <v>5188</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -69121,7 +69127,7 @@
         <v>5046</v>
       </c>
       <c r="C137" t="s">
-        <v>5187</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -69132,7 +69138,7 @@
         <v>5050</v>
       </c>
       <c r="C138" t="s">
-        <v>5188</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -69143,7 +69149,7 @@
         <v>5048</v>
       </c>
       <c r="C139" t="s">
-        <v>5189</v>
+        <v>5191</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -69154,7 +69160,7 @@
         <v>5046</v>
       </c>
       <c r="C140" t="s">
-        <v>5190</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -69165,7 +69171,7 @@
         <v>5052</v>
       </c>
       <c r="C141" t="s">
-        <v>5191</v>
+        <v>5193</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -69176,7 +69182,7 @@
         <v>5050</v>
       </c>
       <c r="C142" t="s">
-        <v>5192</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -69187,7 +69193,7 @@
         <v>5050</v>
       </c>
       <c r="C143" t="s">
-        <v>5193</v>
+        <v>5195</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -69198,7 +69204,7 @@
         <v>5048</v>
       </c>
       <c r="C144" t="s">
-        <v>5194</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -69209,7 +69215,7 @@
         <v>5050</v>
       </c>
       <c r="C145" t="s">
-        <v>5195</v>
+        <v>5197</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -69220,7 +69226,7 @@
         <v>5055</v>
       </c>
       <c r="C146" t="s">
-        <v>5196</v>
+        <v>5198</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -69231,7 +69237,7 @@
         <v>5048</v>
       </c>
       <c r="C147" t="s">
-        <v>5197</v>
+        <v>5199</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -69242,7 +69248,7 @@
         <v>5046</v>
       </c>
       <c r="C148" t="s">
-        <v>5198</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -69253,7 +69259,7 @@
         <v>5046</v>
       </c>
       <c r="C149" t="s">
-        <v>5199</v>
+        <v>5201</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -69264,7 +69270,7 @@
         <v>5048</v>
       </c>
       <c r="C150" t="s">
-        <v>5200</v>
+        <v>5202</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -69275,7 +69281,7 @@
         <v>5052</v>
       </c>
       <c r="C151" t="s">
-        <v>5201</v>
+        <v>5203</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -69286,7 +69292,7 @@
         <v>5052</v>
       </c>
       <c r="C152" t="s">
-        <v>5201</v>
+        <v>5203</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -69297,7 +69303,7 @@
         <v>5046</v>
       </c>
       <c r="C153" t="s">
-        <v>5202</v>
+        <v>5204</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -69308,7 +69314,7 @@
         <v>5046</v>
       </c>
       <c r="C154" t="s">
-        <v>5203</v>
+        <v>5205</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -69319,7 +69325,7 @@
         <v>5046</v>
       </c>
       <c r="C155" t="s">
-        <v>5204</v>
+        <v>5206</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -69450,10 +69456,10 @@
         <v>206</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5205</v>
+        <v>5207</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5206</v>
+        <v>5208</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -69461,10 +69467,10 @@
         <v>13</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>5207</v>
+        <v>5209</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5208</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -69472,10 +69478,10 @@
         <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5209</v>
+        <v>5211</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -69483,10 +69489,10 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5211</v>
+        <v>5213</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -69494,10 +69500,10 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5213</v>
+        <v>5215</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5214</v>
+        <v>5216</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -69505,10 +69511,10 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5215</v>
+        <v>5217</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5216</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -69516,10 +69522,10 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5217</v>
+        <v>5219</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -69527,10 +69533,10 @@
         <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5218</v>
+        <v>5220</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5219</v>
+        <v>5221</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -69538,10 +69544,10 @@
         <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5220</v>
+        <v>5222</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -69549,10 +69555,10 @@
         <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>5223</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>5221</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>5219</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -69560,10 +69566,10 @@
         <v>66</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5222</v>
+        <v>5224</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -69571,10 +69577,10 @@
         <v>70</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5223</v>
+        <v>5225</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>5219</v>
+        <v>5221</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -69582,10 +69588,10 @@
         <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5224</v>
+        <v>5226</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>5216</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -69593,10 +69599,10 @@
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5225</v>
+        <v>5227</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -69604,10 +69610,10 @@
         <v>89</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5226</v>
+        <v>5228</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5227</v>
+        <v>5229</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -69615,10 +69621,10 @@
         <v>98</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5228</v>
+        <v>5230</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5229</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -69626,10 +69632,10 @@
         <v>104</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5230</v>
+        <v>5232</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -69637,10 +69643,10 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5231</v>
+        <v>5233</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -69648,10 +69654,10 @@
         <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5232</v>
+        <v>5234</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -69659,10 +69665,10 @@
         <v>121</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>5233</v>
+        <v>5235</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -69670,10 +69676,10 @@
         <v>126</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5234</v>
+        <v>5236</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -69681,10 +69687,10 @@
         <v>131</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>5235</v>
+        <v>5237</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>5212</v>
+        <v>5214</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -69692,10 +69698,10 @@
         <v>135</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>5236</v>
+        <v>5238</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -69703,10 +69709,10 @@
         <v>139</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>5237</v>
+        <v>5239</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>5238</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -69714,10 +69720,10 @@
         <v>144</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>5239</v>
+        <v>5241</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>5240</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -69725,10 +69731,10 @@
         <v>148</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>5241</v>
+        <v>5243</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>5242</v>
+        <v>5244</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -69736,10 +69742,10 @@
         <v>155</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>5243</v>
+        <v>5245</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>5244</v>
+        <v>5246</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -69747,10 +69753,10 @@
         <v>161</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>5245</v>
+        <v>5247</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>5219</v>
+        <v>5221</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -69758,10 +69764,10 @@
         <v>166</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>5246</v>
+        <v>5248</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -69769,10 +69775,10 @@
         <v>170</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>5247</v>
+        <v>5249</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>5248</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -69780,10 +69786,10 @@
         <v>175</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>5249</v>
+        <v>5251</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -69791,10 +69797,10 @@
         <v>180</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>5250</v>
+        <v>5252</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -69802,10 +69808,10 @@
         <v>185</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>5251</v>
+        <v>5253</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -69813,10 +69819,10 @@
         <v>190</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>5252</v>
+        <v>5254</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>5210</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -69824,10 +69830,10 @@
         <v>194</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>5253</v>
+        <v>5255</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>5254</v>
+        <v>5256</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -69835,10 +69841,10 @@
         <v>198</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>5255</v>
+        <v>5257</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>5229</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -69846,10 +69852,10 @@
         <v>202</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>5256</v>
+        <v>5258</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>5257</v>
+        <v>5259</v>
       </c>
     </row>
   </sheetData>
